--- a/artfynd/A 2212-2025 artfynd.xlsx
+++ b/artfynd/A 2212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112395218</v>
+        <v>112395217</v>
       </c>
       <c r="B2" t="n">
-        <v>78840</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344411</v>
+        <v>344349</v>
       </c>
       <c r="R2" t="n">
-        <v>6601028</v>
+        <v>6601265</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,6 +769,200 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>112395219</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>344458</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6600689</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112395218</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>344411</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6601028</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
